--- a/data/questions/mu_logarit_extraction/Mu_Logarit_112_cau_phan_dang.xlsx
+++ b/data/questions/mu_logarit_extraction/Mu_Logarit_112_cau_phan_dang.xlsx
@@ -567,12 +567,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D53</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Giải bất phương trình lôgarit cơ bản dạng log_a(f(x))&gt;k, f(x) bậc nhất</t>
+          <t>Giải bất phương trình lôgarit cơ bản dạng log_a(f(x))&gt;k</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">

--- a/data/questions/mu_logarit_extraction/Mu_Logarit_112_cau_phan_dang.xlsx
+++ b/data/questions/mu_logarit_extraction/Mu_Logarit_112_cau_phan_dang.xlsx
@@ -1487,12 +1487,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nhận biết công thức lôgarit của lũy thừa log(a^n)=n log a</t>
+          <t>Áp dụng công thức lôgarit của lũy thừa log_a(x^n)=n.log_a(x)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>D70</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nhận biết công thức lôgarit của lũy thừa log_a(a^n)</t>
+          <t>Áp dụng công thức lôgarit của lũy thừa log_a(x^n)=n.log_a(x)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
